--- a/INVENTARIO DE POLOS.xlsx
+++ b/INVENTARIO DE POLOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\klixm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\POLOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A329A22F-824F-432B-982A-F91D17D743B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E1AB29-7F14-4F7F-AF1E-FA3421B1118B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2095" yWindow="1926" windowWidth="12810" windowHeight="17551" activeTab="1" xr2:uid="{B373936B-8CCD-4F7E-AEF5-17EC744A7172}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="38506" windowHeight="19683" activeTab="1" xr2:uid="{B373936B-8CCD-4F7E-AEF5-17EC744A7172}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Clasificación!$A$2:$H$254</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1969,17 +1969,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1998,6 +1989,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2014,119 +2014,7 @@
     <cellStyle name="cf6" xfId="6" xr:uid="{DCEC5AEF-F97A-428A-877B-1E52ED9FF800}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8E8E8"/>
-          <bgColor rgb="FFE8E8E8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE8CF"/>
-          <bgColor rgb="FFCFE8CF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4C7C3"/>
-          <bgColor rgb="FFF4C7C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE8CF"/>
-          <bgColor rgb="FFCFE8CF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4C7C3"/>
-          <bgColor rgb="FFF4C7C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE0F4"/>
-          <bgColor rgb="FFCFE0F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE0F4"/>
-          <bgColor rgb="FFCFE0F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4C7C3"/>
-          <bgColor rgb="FFF4C7C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4C7C3"/>
-          <bgColor rgb="FFF4C7C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEDEDED"/>
-          <bgColor rgb="FFEDEDED"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4C7C3"/>
-          <bgColor rgb="FFF4C7C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE8CF"/>
-          <bgColor rgb="FFCFE8CF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4C7C3"/>
-          <bgColor rgb="FFF4C7C3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2655,6 +2543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E549F01-38B2-4A24-9053-2410A4904A28}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.1640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2662,23 +2551,24 @@
     <col min="2" max="2" width="29.9140625" customWidth="1"/>
     <col min="3" max="3" width="22.4140625" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="6" width="13.08203125" customWidth="1"/>
+    <col min="5" max="5" width="17.25" customWidth="1"/>
+    <col min="6" max="6" width="13.08203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
@@ -2706,7 +2596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>6896</v>
       </c>
@@ -2732,7 +2622,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>6898</v>
       </c>
@@ -2758,7 +2648,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>6899</v>
       </c>
@@ -2784,7 +2674,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>6940</v>
       </c>
@@ -2810,7 +2700,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>6956</v>
       </c>
@@ -2836,7 +2726,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>6970</v>
       </c>
@@ -2862,7 +2752,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>6984</v>
       </c>
@@ -2888,7 +2778,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>6985</v>
       </c>
@@ -2914,7 +2804,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>7014</v>
       </c>
@@ -2940,7 +2830,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>7017</v>
       </c>
@@ -2966,7 +2856,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>7030</v>
       </c>
@@ -2992,7 +2882,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>7062</v>
       </c>
@@ -3018,7 +2908,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>7104</v>
       </c>
@@ -3044,7 +2934,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>7105</v>
       </c>
@@ -3070,7 +2960,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>7107</v>
       </c>
@@ -3096,7 +2986,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <v>7134</v>
       </c>
@@ -3122,7 +3012,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>7164</v>
       </c>
@@ -3148,7 +3038,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <v>7168</v>
       </c>
@@ -3174,7 +3064,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>7209</v>
       </c>
@@ -3200,7 +3090,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <v>7212</v>
       </c>
@@ -3226,7 +3116,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>7213</v>
       </c>
@@ -3252,7 +3142,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
         <v>7225</v>
       </c>
@@ -3278,7 +3168,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>7240</v>
       </c>
@@ -3304,7 +3194,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11">
         <v>7255</v>
       </c>
@@ -3330,7 +3220,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>7256</v>
       </c>
@@ -3356,7 +3246,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11">
         <v>7284</v>
       </c>
@@ -3382,7 +3272,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>7285</v>
       </c>
@@ -3408,7 +3298,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11">
         <v>7288</v>
       </c>
@@ -3434,7 +3324,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>7315</v>
       </c>
@@ -3460,7 +3350,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11">
         <v>7317</v>
       </c>
@@ -3486,7 +3376,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>7329</v>
       </c>
@@ -3512,7 +3402,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11">
         <v>7330</v>
       </c>
@@ -3538,7 +3428,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>7375</v>
       </c>
@@ -3564,7 +3454,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11">
         <v>7376</v>
       </c>
@@ -3590,7 +3480,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>7404</v>
       </c>
@@ -3616,7 +3506,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11">
         <v>7435</v>
       </c>
@@ -3642,7 +3532,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>7724</v>
       </c>
@@ -3668,7 +3558,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11">
         <v>7988</v>
       </c>
@@ -3694,7 +3584,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>7990</v>
       </c>
@@ -3720,7 +3610,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="11">
         <v>7992</v>
       </c>
@@ -3746,7 +3636,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>8005</v>
       </c>
@@ -3772,7 +3662,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="11">
         <v>8007</v>
       </c>
@@ -3798,7 +3688,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>8019</v>
       </c>
@@ -3824,7 +3714,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="11">
         <v>8020</v>
       </c>
@@ -3850,7 +3740,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>8021</v>
       </c>
@@ -3876,7 +3766,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="11">
         <v>8022</v>
       </c>
@@ -3904,7 +3794,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>8023</v>
       </c>
@@ -3930,7 +3820,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="11">
         <v>8050</v>
       </c>
@@ -3956,7 +3846,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>8051</v>
       </c>
@@ -3982,7 +3872,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="11">
         <v>8052</v>
       </c>
@@ -4008,7 +3898,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>8053</v>
       </c>
@@ -4034,7 +3924,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="11">
         <v>8066</v>
       </c>
@@ -4060,7 +3950,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>8067</v>
       </c>
@@ -4086,7 +3976,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="11">
         <v>8068</v>
       </c>
@@ -4112,7 +4002,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>8069</v>
       </c>
@@ -4138,7 +4028,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="11">
         <v>8079</v>
       </c>
@@ -4164,7 +4054,7 @@
         <v>Revisar</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>8080</v>
       </c>
@@ -4190,7 +4080,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="11">
         <v>8081</v>
       </c>
@@ -4216,7 +4106,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>8082</v>
       </c>
@@ -4242,7 +4132,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="11">
         <v>8083</v>
       </c>
@@ -4268,7 +4158,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>8094</v>
       </c>
@@ -4294,7 +4184,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="11">
         <v>8095</v>
       </c>
@@ -4320,7 +4210,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>8096</v>
       </c>
@@ -4346,7 +4236,7 @@
         <v>Revisar</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="11">
         <v>8097</v>
       </c>
@@ -4372,7 +4262,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>8108</v>
       </c>
@@ -4398,7 +4288,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="11">
         <v>8112</v>
       </c>
@@ -4424,7 +4314,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>8124</v>
       </c>
@@ -4450,7 +4340,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="11">
         <v>8139</v>
       </c>
@@ -4476,7 +4366,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>8140</v>
       </c>
@@ -4502,7 +4392,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="11">
         <v>8141</v>
       </c>
@@ -4528,7 +4418,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>8142</v>
       </c>
@@ -4554,7 +4444,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="11">
         <v>8143</v>
       </c>
@@ -4580,7 +4470,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>8144</v>
       </c>
@@ -4606,7 +4496,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="11">
         <v>8183</v>
       </c>
@@ -4632,7 +4522,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>8184</v>
       </c>
@@ -4658,7 +4548,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="11">
         <v>8187</v>
       </c>
@@ -4684,7 +4574,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>8199</v>
       </c>
@@ -4710,7 +4600,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="11">
         <v>8201</v>
       </c>
@@ -4736,7 +4626,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>8203</v>
       </c>
@@ -4762,7 +4652,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="11">
         <v>8213</v>
       </c>
@@ -4788,7 +4678,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>8214</v>
       </c>
@@ -4814,7 +4704,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="11">
         <v>8215</v>
       </c>
@@ -4840,7 +4730,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>8216</v>
       </c>
@@ -4866,7 +4756,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="11">
         <v>8217</v>
       </c>
@@ -4892,7 +4782,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>8218</v>
       </c>
@@ -4918,7 +4808,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="11">
         <v>8219</v>
       </c>
@@ -4944,7 +4834,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>11604</v>
       </c>
@@ -4970,7 +4860,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="11">
         <v>11611</v>
       </c>
@@ -4996,7 +4886,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>11621</v>
       </c>
@@ -5022,7 +4912,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="11">
         <v>11622</v>
       </c>
@@ -5048,7 +4938,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="7">
         <v>11623</v>
       </c>
@@ -5076,7 +4966,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="11">
         <v>11625</v>
       </c>
@@ -5102,7 +4992,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="7">
         <v>11627</v>
       </c>
@@ -5128,7 +5018,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="11">
         <v>11631</v>
       </c>
@@ -5154,7 +5044,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="7">
         <v>11635</v>
       </c>
@@ -5180,7 +5070,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="11">
         <v>11636</v>
       </c>
@@ -5206,7 +5096,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="7">
         <v>11640</v>
       </c>
@@ -5232,7 +5122,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="11">
         <v>11643</v>
       </c>
@@ -5258,7 +5148,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="7">
         <v>11645</v>
       </c>
@@ -5284,7 +5174,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="11">
         <v>11646</v>
       </c>
@@ -5310,7 +5200,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7">
         <v>11649</v>
       </c>
@@ -5336,7 +5226,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="11">
         <v>11653</v>
       </c>
@@ -5362,7 +5252,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7">
         <v>11654</v>
       </c>
@@ -5388,7 +5278,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="11">
         <v>11658</v>
       </c>
@@ -5414,7 +5304,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="11"/>
       <c r="B107" s="7" t="s">
         <v>231</v>
@@ -5438,7 +5328,7 @@
         <v>Revisar</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7">
         <v>11659</v>
       </c>
@@ -5464,7 +5354,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="11">
         <v>11663</v>
       </c>
@@ -5490,7 +5380,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7">
         <v>11665</v>
       </c>
@@ -5516,7 +5406,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="11">
         <v>11667</v>
       </c>
@@ -5542,7 +5432,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7">
         <v>11676</v>
       </c>
@@ -5568,7 +5458,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="11">
         <v>11682</v>
       </c>
@@ -5594,7 +5484,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7">
         <v>11685</v>
       </c>
@@ -5620,7 +5510,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="11">
         <v>11689</v>
       </c>
@@ -5646,7 +5536,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7">
         <v>11694</v>
       </c>
@@ -5672,7 +5562,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="11">
         <v>11700</v>
       </c>
@@ -5698,7 +5588,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7">
         <v>11701</v>
       </c>
@@ -5724,7 +5614,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="11">
         <v>11703</v>
       </c>
@@ -5750,7 +5640,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7">
         <v>11707</v>
       </c>
@@ -5776,7 +5666,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="11">
         <v>11708</v>
       </c>
@@ -5802,7 +5692,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7">
         <v>11720</v>
       </c>
@@ -5828,7 +5718,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="11">
         <v>11721</v>
       </c>
@@ -5854,7 +5744,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
         <v>11724</v>
       </c>
@@ -5880,7 +5770,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="11">
         <v>11725</v>
       </c>
@@ -5906,7 +5796,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7">
         <v>11726</v>
       </c>
@@ -5932,7 +5822,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="11">
         <v>12890</v>
       </c>
@@ -5958,7 +5848,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="7">
         <v>12891</v>
       </c>
@@ -5984,7 +5874,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="11">
         <v>12907</v>
       </c>
@@ -6010,7 +5900,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="7">
         <v>12948</v>
       </c>
@@ -6036,7 +5926,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="11">
         <v>12950</v>
       </c>
@@ -6062,7 +5952,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="7">
         <v>12951</v>
       </c>
@@ -6088,7 +5978,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="11">
         <v>13144</v>
       </c>
@@ -6114,7 +6004,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="7">
         <v>13146</v>
       </c>
@@ -6140,7 +6030,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="11">
         <v>13612</v>
       </c>
@@ -6166,7 +6056,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="7">
         <v>13615</v>
       </c>
@@ -6192,7 +6082,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="11">
         <v>13617</v>
       </c>
@@ -6218,7 +6108,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7">
         <v>13619</v>
       </c>
@@ -6244,7 +6134,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="11">
         <v>15145</v>
       </c>
@@ -6270,7 +6160,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7">
         <v>15147</v>
       </c>
@@ -6296,7 +6186,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="11">
         <v>15575</v>
       </c>
@@ -6322,7 +6212,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="7">
         <v>15589</v>
       </c>
@@ -6348,7 +6238,7 @@
         <v>Revisar</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="11">
         <v>15590</v>
       </c>
@@ -6374,7 +6264,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="7">
         <v>15591</v>
       </c>
@@ -6400,7 +6290,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="11">
         <v>15592</v>
       </c>
@@ -6426,7 +6316,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7">
         <v>15784</v>
       </c>
@@ -6452,7 +6342,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="11">
         <v>15786</v>
       </c>
@@ -6478,7 +6368,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7">
         <v>15918</v>
       </c>
@@ -6504,7 +6394,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="11">
         <v>15919</v>
       </c>
@@ -6530,7 +6420,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7">
         <v>15920</v>
       </c>
@@ -6556,7 +6446,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="11">
         <v>15922</v>
       </c>
@@ -6582,7 +6472,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7">
         <v>15923</v>
       </c>
@@ -6608,7 +6498,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="11">
         <v>16113</v>
       </c>
@@ -6634,7 +6524,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7">
         <v>16118</v>
       </c>
@@ -6660,7 +6550,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="11">
         <v>17045</v>
       </c>
@@ -6686,7 +6576,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7">
         <v>17060</v>
       </c>
@@ -6712,7 +6602,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="11">
         <v>17061</v>
       </c>
@@ -6738,7 +6628,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7">
         <v>17063</v>
       </c>
@@ -6764,7 +6654,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="11">
         <v>17077</v>
       </c>
@@ -6790,7 +6680,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7">
         <v>17088</v>
       </c>
@@ -6816,7 +6706,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="11">
         <v>17104</v>
       </c>
@@ -6842,7 +6732,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7">
         <v>17105</v>
       </c>
@@ -6868,7 +6758,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="11">
         <v>17106</v>
       </c>
@@ -6894,7 +6784,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7">
         <v>17107</v>
       </c>
@@ -6920,7 +6810,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="11">
         <v>17299</v>
       </c>
@@ -6946,7 +6836,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7">
         <v>17300</v>
       </c>
@@ -6972,7 +6862,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="11">
         <v>18515</v>
       </c>
@@ -6998,7 +6888,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7">
         <v>18516</v>
       </c>
@@ -7024,7 +6914,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="11">
         <v>18517</v>
       </c>
@@ -7050,7 +6940,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7">
         <v>18518</v>
       </c>
@@ -7076,7 +6966,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="11">
         <v>18714</v>
       </c>
@@ -7102,7 +6992,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7">
         <v>18844</v>
       </c>
@@ -7128,7 +7018,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="11">
         <v>18845</v>
       </c>
@@ -7154,7 +7044,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7">
         <v>18846</v>
       </c>
@@ -7180,7 +7070,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="11">
         <v>18847</v>
       </c>
@@ -7206,7 +7096,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7">
         <v>19039</v>
       </c>
@@ -7232,7 +7122,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="11">
         <v>19040</v>
       </c>
@@ -7258,7 +7148,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7">
         <v>19041</v>
       </c>
@@ -7284,7 +7174,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="11">
         <v>19042</v>
       </c>
@@ -7310,7 +7200,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7">
         <v>19043</v>
       </c>
@@ -7336,7 +7226,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="11">
         <v>19175</v>
       </c>
@@ -7362,7 +7252,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7">
         <v>19178</v>
       </c>
@@ -7388,7 +7278,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="11">
         <v>19490</v>
       </c>
@@ -7414,7 +7304,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7">
         <v>19491</v>
       </c>
@@ -7440,7 +7330,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="11">
         <v>19492</v>
       </c>
@@ -7466,7 +7356,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7">
         <v>19493</v>
       </c>
@@ -7492,7 +7382,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="11">
         <v>19494</v>
       </c>
@@ -7518,7 +7408,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7">
         <v>19776</v>
       </c>
@@ -7544,7 +7434,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="11">
         <v>19777</v>
       </c>
@@ -7570,7 +7460,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7">
         <v>19778</v>
       </c>
@@ -7596,7 +7486,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="11">
         <v>19779</v>
       </c>
@@ -7622,7 +7512,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7">
         <v>19780</v>
       </c>
@@ -7648,7 +7538,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="11">
         <v>19781</v>
       </c>
@@ -7674,7 +7564,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7">
         <v>19782</v>
       </c>
@@ -7700,7 +7590,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="11">
         <v>19792</v>
       </c>
@@ -7718,15 +7608,15 @@
       </c>
       <c r="F195" s="9"/>
       <c r="G195" s="8">
-        <f t="shared" ref="G195:G258" si="6">D195-E195-F195</f>
+        <f t="shared" ref="G195:G254" si="6">D195-E195-F195</f>
         <v>0</v>
       </c>
       <c r="H195" s="10" t="str">
-        <f t="shared" ref="H195:H258" si="7">IF(AND(E195="",F195=""),"Sin revisar",IF(G195=0,"Clasificado","Revisar"))</f>
-        <v>Clasificado</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H195:H254" si="7">IF(AND(E195="",F195=""),"Sin revisar",IF(G195=0,"Clasificado","Revisar"))</f>
+        <v>Clasificado</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7">
         <v>19793</v>
       </c>
@@ -7752,7 +7642,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="11">
         <v>19794</v>
       </c>
@@ -7778,7 +7668,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7">
         <v>19795</v>
       </c>
@@ -7804,7 +7694,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="11">
         <v>19797</v>
       </c>
@@ -7830,7 +7720,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7">
         <v>19807</v>
       </c>
@@ -7856,7 +7746,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="11">
         <v>19808</v>
       </c>
@@ -7882,7 +7772,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7">
         <v>19809</v>
       </c>
@@ -7908,7 +7798,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="11">
         <v>19810</v>
       </c>
@@ -7934,7 +7824,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="7">
         <v>19823</v>
       </c>
@@ -7960,7 +7850,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="11">
         <v>19824</v>
       </c>
@@ -7986,7 +7876,7 @@
         <v>Revisar</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="7">
         <v>19825</v>
       </c>
@@ -8012,7 +7902,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="11">
         <v>19827</v>
       </c>
@@ -8038,7 +7928,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="7">
         <v>19837</v>
       </c>
@@ -8064,7 +7954,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="11">
         <v>19840</v>
       </c>
@@ -8090,7 +7980,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="7">
         <v>20032</v>
       </c>
@@ -8116,7 +8006,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="11">
         <v>20034</v>
       </c>
@@ -8142,7 +8032,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="7">
         <v>20035</v>
       </c>
@@ -8168,7 +8058,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="11">
         <v>20036</v>
       </c>
@@ -8194,7 +8084,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="7">
         <v>20048</v>
       </c>
@@ -8220,7 +8110,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="11">
         <v>20050</v>
       </c>
@@ -8246,7 +8136,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="7">
         <v>20051</v>
       </c>
@@ -8272,7 +8162,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="11">
         <v>20063</v>
       </c>
@@ -8298,7 +8188,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="7">
         <v>20064</v>
       </c>
@@ -8324,7 +8214,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="11">
         <v>20065</v>
       </c>
@@ -8350,7 +8240,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="7">
         <v>20078</v>
       </c>
@@ -8376,7 +8266,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="11">
         <v>20079</v>
       </c>
@@ -8402,7 +8292,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="7">
         <v>20082</v>
       </c>
@@ -8428,7 +8318,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="11">
         <v>20096</v>
       </c>
@@ -8454,7 +8344,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="7">
         <v>20097</v>
       </c>
@@ -8480,7 +8370,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="11">
         <v>20107</v>
       </c>
@@ -8506,7 +8396,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="7">
         <v>20109</v>
       </c>
@@ -8532,7 +8422,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="11">
         <v>20110</v>
       </c>
@@ -8558,7 +8448,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="7">
         <v>20112</v>
       </c>
@@ -8584,7 +8474,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="11">
         <v>20125</v>
       </c>
@@ -8610,7 +8500,7 @@
         <v>Clasificado</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="7">
         <v>20127</v>
       </c>
@@ -9261,7 +9151,36 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H254" xr:uid="{F17A2440-8ADA-4319-A246-06BBD7564B18}"/>
+  <autoFilter ref="A2:H254" xr:uid="{F17A2440-8ADA-4319-A246-06BBD7564B18}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="B TEX 4 MC NEGRO ROJO L"/>
+        <filter val="B TEX 4 ML NEGRO VERDE 2XL"/>
+        <filter val="B TEX 4 ML NEGRO VERDE S"/>
+        <filter val="B TEX C MC NEGRO ROJO 2XL"/>
+        <filter val="B TEX C MC NEGRO ROJO 3XL"/>
+        <filter val="B TEX C MC NEGRO ROJO L"/>
+        <filter val="B TEX C MC NEGRO VERDE S"/>
+        <filter val="B TEX C MC ROJO NEGRO 2XL"/>
+        <filter val="B TEX C MC ROJO NEGRO 3XL"/>
+        <filter val="B TEX C ML NEGRO BLANCO 2XL"/>
+        <filter val="B TEX C ML NEGRO BLANCO 3XL"/>
+        <filter val="B TEX C ML NEGRO BLANCO L"/>
+        <filter val="B TEX C ML NEGRO BLANCO M"/>
+        <filter val="B TEX C ML NEGRO BLANCO S"/>
+        <filter val="B TEX C ML NEGRO BLANCO XL"/>
+        <filter val="B TEX C ML NEGRO ROJO 3XL"/>
+        <filter val="B TEX C ML NEGRO ROJO L"/>
+        <filter val="B TEX C ML NEGRO ROJO M"/>
+        <filter val="B TEX C ML NEGRO ROJO S"/>
+        <filter val="B TEX C ML NEGRO ROJO XL"/>
+        <filter val="B TEX C ML NEGRO VERDE L"/>
+        <filter val="B TEX C ML NEGRO VERDE M"/>
+        <filter val="B TEX C ML NEGRO VERDE S"/>
+        <filter val="B TEX C ML NEGRO VERDE XL"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -9269,25 +9188,19 @@
     <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H254">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
-      <formula>H3="Clasificado"</formula>
+    <cfRule type="expression" dxfId="12" priority="2" stopIfTrue="1">
+      <formula>AND(E3="",F3="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H254">
-    <cfRule type="expression" dxfId="11" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="3" stopIfTrue="1">
+      <formula>H3="Clasificado"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="4" stopIfTrue="1">
       <formula>H3="Revisar"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H254">
-    <cfRule type="expression" dxfId="10" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="5" stopIfTrue="1">
       <formula>H3="Sin revisar"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G254">
-    <cfRule type="expression" dxfId="9" priority="2" stopIfTrue="1">
-      <formula>AND(E3="",F3="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -9313,10 +9226,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -9367,7 +9280,7 @@
       <c r="A8" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <f>IFERROR(B5/(B5+B6),0)</f>
         <v>0.98248407643312097</v>
       </c>
@@ -9376,7 +9289,7 @@
       <c r="A9" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <f>IFERROR(B6/(B5+B6),0)</f>
         <v>1.751592356687898E-2</v>
       </c>
@@ -9412,36 +9325,36 @@
       <c r="A13" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <f>IFERROR((B3-B12)/B3,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9469,15 +9382,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="22" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
@@ -9503,7 +9416,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="15" t="s">
         <v>547</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -9523,13 +9436,13 @@
         <f t="shared" ref="F3:F23" si="1">IF(E3="","",IF(D3="","Sin inicial",D3-E3))</f>
         <v>0</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="16">
         <f t="shared" ref="G3:G23" si="2">IF(E3="","",IF(OR(D3="",D3=0),"Nuevo color",E3/D3))</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>547</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -9539,7 +9452,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="18">
         <v>67</v>
       </c>
       <c r="E4" s="9">
@@ -9549,13 +9462,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="15" t="s">
         <v>550</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -9575,13 +9488,13 @@
         <f t="shared" si="1"/>
         <v>-12.399999999999999</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="16">
         <f t="shared" si="2"/>
         <v>1.4428571428571428</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -9591,7 +9504,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="18">
         <v>62</v>
       </c>
       <c r="E6" s="9">
@@ -9601,13 +9514,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="15" t="s">
         <v>552</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -9627,13 +9540,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="15" t="s">
         <v>555</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -9653,13 +9566,13 @@
         <f t="shared" si="1"/>
         <v>-59.5</v>
       </c>
-      <c r="G8" s="19" t="str">
+      <c r="G8" s="16" t="str">
         <f t="shared" si="2"/>
         <v>Nuevo color</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="15" t="s">
         <v>555</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -9679,13 +9592,13 @@
         <f t="shared" si="1"/>
         <v>-66.849999999999994</v>
       </c>
-      <c r="G9" s="19" t="str">
+      <c r="G9" s="16" t="str">
         <f t="shared" si="2"/>
         <v>Nuevo color</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>555</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -9695,7 +9608,7 @@
         <f t="shared" si="0"/>
         <v>Tela nueva</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="18">
         <v>50</v>
       </c>
       <c r="E10" s="9">
@@ -9705,13 +9618,13 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="16">
         <f t="shared" si="2"/>
         <v>0.96</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="15" t="s">
         <v>555</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -9731,13 +9644,13 @@
         <f t="shared" si="1"/>
         <v>-62.499999999999993</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="16">
         <f t="shared" si="2"/>
         <v>2.7556179775280896</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>555</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -9747,7 +9660,7 @@
         <f t="shared" si="0"/>
         <v>Tela nueva</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="18">
         <v>45</v>
       </c>
       <c r="E12" s="9">
@@ -9757,13 +9670,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="15" t="s">
         <v>555</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -9783,13 +9696,13 @@
         <f t="shared" si="1"/>
         <v>-41</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="16">
         <f t="shared" si="2"/>
         <v>2.3666666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -9799,7 +9712,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="18">
         <v>40</v>
       </c>
       <c r="E14" s="9">
@@ -9809,13 +9722,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="15" t="s">
         <v>552</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -9835,13 +9748,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -9851,7 +9764,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="18">
         <v>15</v>
       </c>
       <c r="E16" s="9">
@@ -9861,13 +9774,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="15" t="s">
         <v>552</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -9887,13 +9800,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -9903,7 +9816,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="18">
         <v>15</v>
       </c>
       <c r="E18" s="9">
@@ -9913,13 +9826,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="15" t="s">
         <v>552</v>
       </c>
       <c r="B19" s="7" t="s">
@@ -9939,13 +9852,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -9955,7 +9868,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="18">
         <v>50</v>
       </c>
       <c r="E20" s="9">
@@ -9965,13 +9878,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="15" t="s">
         <v>552</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -9991,13 +9904,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -10007,7 +9920,7 @@
         <f t="shared" si="0"/>
         <v>Tela antigua</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="18">
         <v>10</v>
       </c>
       <c r="E22" s="9">
@@ -10017,13 +9930,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="15" t="s">
         <v>552</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -10043,7 +9956,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -10055,42 +9968,42 @@
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="22">
+      <c r="D25" s="19">
         <f>SUM(D3:D23)</f>
         <v>754.6</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="19">
         <f>SUM(E3:E23)</f>
         <v>994.85</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="19">
         <f>SUM(F3:F23)</f>
         <v>-240.25</v>
       </c>
       <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:7" s="24" customFormat="1" ht="53.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="23" t="s">
+    <row r="27" spans="1:7" s="21" customFormat="1" ht="53.3" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="20" t="s">
         <v>569</v>
       </c>
       <c r="B27" s="8">
         <f>SUMIF(C3:C23,"Tela nueva",D3:D23)</f>
         <v>188.6</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="21" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="24" customFormat="1" ht="58.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="23" t="s">
+    <row r="28" spans="1:7" s="21" customFormat="1" ht="58.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="20" t="s">
         <v>571</v>
       </c>
       <c r="B28" s="8">
         <f>SUMIF(C3:C23,"Tela antigua",D3:D23)</f>
         <v>566</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="21" t="s">
         <v>572</v>
       </c>
     </row>
@@ -10134,43 +10047,35 @@
     <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
       <formula>C3="Tela antigua"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C23">
-    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
-      <formula>C3="Tela antigua"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C22">
-    <cfRule type="expression" dxfId="6" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="9" stopIfTrue="1">
       <formula>C3="Tela nueva"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C23">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>C3="Tela antigua"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>C3="Tela nueva"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G22">
-    <cfRule type="expression" dxfId="4" priority="11" stopIfTrue="1">
-      <formula>AND(G3&lt;&gt;"",G3&lt;0.15)</formula>
+  <conditionalFormatting sqref="F3:F23">
+    <cfRule type="expression" dxfId="4" priority="10" stopIfTrue="1">
+      <formula>AND(ISNUMBER(F3),F3&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F23">
-    <cfRule type="expression" dxfId="3" priority="10" stopIfTrue="1">
-      <formula>AND(ISNUMBER(F3),F3&lt;0)</formula>
+  <conditionalFormatting sqref="G3:G22">
+    <cfRule type="expression" dxfId="3" priority="11" stopIfTrue="1">
+      <formula>AND(G3&lt;&gt;"",G3&lt;0.15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G23">
     <cfRule type="expression" dxfId="2" priority="12" stopIfTrue="1">
       <formula>AND(ISNUMBER(G3),G3&lt;0.15)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G23">
     <cfRule type="expression" dxfId="1" priority="13" stopIfTrue="1">
       <formula>AND(ISNUMBER(G3),G3&gt;1)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G23">
     <cfRule type="expression" dxfId="0" priority="14" stopIfTrue="1">
       <formula>ISTEXT(G3)</formula>
     </cfRule>
